--- a/학습계획.xlsx
+++ b/학습계획.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="파이토치 학습계획" sheetId="1" r:id="R30435be895c7470d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="파이토치 학습계획" sheetId="1" r:id="R91d0e22751b74d1a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -17,7 +17,7 @@
     <x:numFmt numFmtId="200" formatCode="mm/dd"/>
     <x:numFmt numFmtId="201" formatCode="0.0"/>
   </x:numFmts>
-  <x:fonts count="3">
+  <x:fonts count="4">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -33,8 +33,14 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="NanumGothic"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF243247"/>
+      <x:name val="NanumGothic"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="8">
+  <x:fills count="11">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -69,6 +75,21 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFF4F0FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF274C77"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEFF4F9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF7F9FC"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -84,7 +105,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="29">
+  <x:cellXfs count="41">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -166,6 +187,40 @@
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="201" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -636,6 +691,229 @@
       </x:c>
       <x:c r="G12" s="28"/>
     </x:row>
+    <x:row r="14" ht="30" customHeight="1">
+      <x:c r="A14" s="29" t="str">
+        <x:v>혼공 머신러닝·딥러닝 — 이론 (1~9장)</x:v>
+      </x:c>
+      <x:c r="B14" s="29"/>
+      <x:c r="C14" s="29"/>
+      <x:c r="D14" s="29"/>
+      <x:c r="E14" s="29"/>
+      <x:c r="F14" s="29"/>
+      <x:c r="G14" s="29"/>
+    </x:row>
+    <x:row r="15" ht="28" customHeight="1">
+      <x:c r="A15" s="32" t="str">
+        <x:v>날짜</x:v>
+      </x:c>
+      <x:c r="B15" s="32" t="str">
+        <x:v>요일</x:v>
+      </x:c>
+      <x:c r="C15" s="32" t="str">
+        <x:v>장</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="str">
+        <x:v>진도 목표</x:v>
+      </x:c>
+      <x:c r="E15" s="32" t="str">
+        <x:v>학습 내용</x:v>
+      </x:c>
+      <x:c r="F15" s="32" t="str">
+        <x:v>계획(h)</x:v>
+      </x:c>
+      <x:c r="G15" s="32" t="str">
+        <x:v>실제(h)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="34" customHeight="1">
+      <x:c r="A16" s="33" t="d">
+        <x:v>2026-10-28T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B16" s="34" t="str">
+        <x:v>수</x:v>
+      </x:c>
+      <x:c r="C16" s="34" t="str">
+        <x:v>1장</x:v>
+      </x:c>
+      <x:c r="D16" s="34" t="str">
+        <x:v>이론 훑기</x:v>
+      </x:c>
+      <x:c r="E16" s="35" t="str">
+        <x:v>머신러닝 개념 / 첫 모델의 흐름</x:v>
+      </x:c>
+      <x:c r="F16" s="36" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G16" s="36"/>
+    </x:row>
+    <x:row r="17" ht="34" customHeight="1">
+      <x:c r="A17" s="37" t="d">
+        <x:v>2026-10-29T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B17" s="38" t="str">
+        <x:v>목</x:v>
+      </x:c>
+      <x:c r="C17" s="38" t="str">
+        <x:v>2장</x:v>
+      </x:c>
+      <x:c r="D17" s="38" t="str">
+        <x:v>이론 훑기</x:v>
+      </x:c>
+      <x:c r="E17" s="39" t="str">
+        <x:v>훈련·테스트 세트 / 데이터 전처리</x:v>
+      </x:c>
+      <x:c r="F17" s="40" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G17" s="40"/>
+    </x:row>
+    <x:row r="18" ht="34" customHeight="1">
+      <x:c r="A18" s="33" t="d">
+        <x:v>2026-10-30T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B18" s="34" t="str">
+        <x:v>금</x:v>
+      </x:c>
+      <x:c r="C18" s="34" t="str">
+        <x:v>3장</x:v>
+      </x:c>
+      <x:c r="D18" s="34" t="str">
+        <x:v>이론 훑기</x:v>
+      </x:c>
+      <x:c r="E18" s="35" t="str">
+        <x:v>최근접 이웃 / 선형 회귀 / 특성 공학·규제</x:v>
+      </x:c>
+      <x:c r="F18" s="36" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G18" s="36"/>
+    </x:row>
+    <x:row r="19" ht="34" customHeight="1">
+      <x:c r="A19" s="37" t="d">
+        <x:v>2026-10-31T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B19" s="38" t="str">
+        <x:v>토</x:v>
+      </x:c>
+      <x:c r="C19" s="38" t="str">
+        <x:v>4장</x:v>
+      </x:c>
+      <x:c r="D19" s="38" t="str">
+        <x:v>이론 훑기</x:v>
+      </x:c>
+      <x:c r="E19" s="39" t="str">
+        <x:v>로지스틱 회귀 / 확률적 경사 하강법</x:v>
+      </x:c>
+      <x:c r="F19" s="40" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G19" s="40"/>
+    </x:row>
+    <x:row r="20" ht="34" customHeight="1">
+      <x:c r="A20" s="33" t="d">
+        <x:v>2026-11-01T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B20" s="34" t="str">
+        <x:v>일</x:v>
+      </x:c>
+      <x:c r="C20" s="34" t="str">
+        <x:v>5장</x:v>
+      </x:c>
+      <x:c r="D20" s="34" t="str">
+        <x:v>이론 훑기</x:v>
+      </x:c>
+      <x:c r="E20" s="35" t="str">
+        <x:v>결정 트리 / 교차 검증 / 앙상블</x:v>
+      </x:c>
+      <x:c r="F20" s="36" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G20" s="36"/>
+    </x:row>
+    <x:row r="21" ht="34" customHeight="1">
+      <x:c r="A21" s="37" t="d">
+        <x:v>2026-11-02T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B21" s="38" t="str">
+        <x:v>월</x:v>
+      </x:c>
+      <x:c r="C21" s="38" t="str">
+        <x:v>6장</x:v>
+      </x:c>
+      <x:c r="D21" s="38" t="str">
+        <x:v>이론 훑기</x:v>
+      </x:c>
+      <x:c r="E21" s="39" t="str">
+        <x:v>군집 / K-means / 주성분 분석(PCA)</x:v>
+      </x:c>
+      <x:c r="F21" s="40" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G21" s="40"/>
+    </x:row>
+    <x:row r="22" ht="34" customHeight="1">
+      <x:c r="A22" s="33" t="d">
+        <x:v>2026-11-03T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B22" s="34" t="str">
+        <x:v>화</x:v>
+      </x:c>
+      <x:c r="C22" s="34" t="str">
+        <x:v>7장</x:v>
+      </x:c>
+      <x:c r="D22" s="34" t="str">
+        <x:v>이론 훑기</x:v>
+      </x:c>
+      <x:c r="E22" s="35" t="str">
+        <x:v>인공 신경망 / 심층 신경망 / 모델 훈련</x:v>
+      </x:c>
+      <x:c r="F22" s="36" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G22" s="36"/>
+    </x:row>
+    <x:row r="23" ht="34" customHeight="1">
+      <x:c r="A23" s="37" t="d">
+        <x:v>2026-11-04T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B23" s="38" t="str">
+        <x:v>수</x:v>
+      </x:c>
+      <x:c r="C23" s="38" t="str">
+        <x:v>8장</x:v>
+      </x:c>
+      <x:c r="D23" s="38" t="str">
+        <x:v>이론 훑기</x:v>
+      </x:c>
+      <x:c r="E23" s="39" t="str">
+        <x:v>합성곱 신경망(CNN) / 이미지 분류·시각화</x:v>
+      </x:c>
+      <x:c r="F23" s="40" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G23" s="40"/>
+    </x:row>
+    <x:row r="24" ht="34" customHeight="1">
+      <x:c r="A24" s="33" t="d">
+        <x:v>2026-11-05T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B24" s="34" t="str">
+        <x:v>목</x:v>
+      </x:c>
+      <x:c r="C24" s="34" t="str">
+        <x:v>9장</x:v>
+      </x:c>
+      <x:c r="D24" s="34" t="str">
+        <x:v>이론 훑기</x:v>
+      </x:c>
+      <x:c r="E24" s="35" t="str">
+        <x:v>순환 신경망(RNN) / LSTM·GRU</x:v>
+      </x:c>
+      <x:c r="F24" s="36" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G24" s="36"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/학습계획.xlsx
+++ b/학습계획.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="파이토치 학습계획" sheetId="1" r:id="Ra7945532ee904276"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="파이토치 학습계획" sheetId="1" r:id="Rc21539fefb7a47d0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -639,7 +639,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G2" s="5" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="34.04999923706055" customHeight="1">
@@ -905,7 +905,9 @@
       <x:c r="F16" s="27">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G16" s="27"/>
+      <x:c r="G16" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="34.04999923706055" customHeight="1">
       <x:c r="A17" s="28">

--- a/학습계획.xlsx
+++ b/학습계획.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="파이토치 학습계획" sheetId="1" r:id="Rc21539fefb7a47d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="파이토치 학습계획" sheetId="1" r:id="R85ace5641ac7465e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -661,7 +661,9 @@
       <x:c r="F3" s="9">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G3" s="9"/>
+      <x:c r="G3" s="9" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="34.04999923706055" customHeight="1">
       <x:c r="A4" s="6">
@@ -928,7 +930,9 @@
       <x:c r="F17" s="31">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G17" s="31"/>
+      <x:c r="G17" s="31" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="34.04999923706055" customHeight="1">
       <x:c r="A18" s="24">

--- a/학습계획.xlsx
+++ b/학습계획.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="파이토치 학습계획" sheetId="1" r:id="R85ace5641ac7465e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="파이토치 학습계획" sheetId="1" r:id="R53fc37f61e4d44a3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -684,7 +684,9 @@
       <x:c r="F4" s="9">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G4" s="9"/>
+      <x:c r="G4" s="9" t="n">
+        <x:v>4</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="34.04999923706055" customHeight="1">
       <x:c r="A5" s="10">

--- a/학습계획.xlsx
+++ b/학습계획.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="파이토치 학습계획" sheetId="1" r:id="R53fc37f61e4d44a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="파이토치 학습계획" sheetId="1" r:id="Rea8fa25bb3ff402c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -955,7 +955,9 @@
       <x:c r="F18" s="27">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G18" s="27"/>
+      <x:c r="G18" s="27" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="34.04999923706055" customHeight="1">
       <x:c r="A19" s="28">

--- a/학습계획.xlsx
+++ b/학습계획.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="파이토치 학습계획" sheetId="1" r:id="Rea8fa25bb3ff402c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="파이토치 학습계획" sheetId="1" r:id="Rb413a5360ca64233"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -64,106 +64,97 @@
     <x:t xml:space="preserve">당뇨병 예측 마무리 / 붓꽃 분류</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">Part 4</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">첫째 날</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">객체 탐지로 마스크 인식하기</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">둘째 날</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">오토인코더 노이즈 제거 / U-Net 시작</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">나머지 완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">U-Net 마무리 / 숫자 이미지 생성</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Part 5</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">RNN 비트코인 가격 예측</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">문자 RNN 자연어 품사 태깅</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">최종 완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">트랜스포머 객체명 인식 / 정리</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">혼공 머신러닝·딥러닝 — 이론 (1~9장)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">장</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1장</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">이론 훑기</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">머신러닝 개념 / 첫 모델의 흐름</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">2장</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">훈련·테스트 세트 / 데이터 전처리</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">3장</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">최근접 이웃 / 선형 회귀 / 특성 공학·규제</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">토</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Part 3</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">CNN / VGG·ResNet / 개 품종 분류 일부</x:t>
+    <x:t xml:space="preserve">4장</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">로지스틱 회귀 / 확률적 경사 하강법</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">일</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">개 품종 마무리 / 흉부 X-ray / 자연 풍경</x:t>
+    <x:t xml:space="preserve">5장</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">결정 트리 / 교차 검증 / 앙상블</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">월</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Part 4</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">첫째 날</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">객체 탐지로 마스크 인식하기</x:t>
+    <x:t xml:space="preserve">6장</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">군집 / K-means / 주성분 분석(PCA)</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">화</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">둘째 날</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">오토인코더 노이즈 제거 / U-Net 시작</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">나머지 완료</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">U-Net 마무리 / 숫자 이미지 생성</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Part 5</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">RNN 비트코인 가격 예측</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">문자 RNN 자연어 품사 태깅</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">최종 완료</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">트랜스포머 객체명 인식 / 정리</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">혼공 머신러닝·딥러닝 — 이론 (1~9장)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">장</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">1장</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">이론 훑기</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">머신러닝 개념 / 첫 모델의 흐름</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">2장</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">훈련·테스트 세트 / 데이터 전처리</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">3장</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">최근접 이웃 / 선형 회귀 / 특성 공학·규제</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">4장</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">로지스틱 회귀 / 확률적 경사 하강법</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">5장</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">결정 트리 / 교차 검증 / 앙상블</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">6장</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">군집 / K-means / 주성분 분석(PCA)</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">7장</x:t>
@@ -289,7 +280,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="54">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
@@ -380,6 +371,70 @@
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="176" fontId="1" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="58" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="176" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="58" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="176" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="58" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="176" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="58" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="176" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="58" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="176" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -689,401 +744,435 @@
       </x:c>
     </x:row>
     <x:row r="5" ht="34.04999923706055" customHeight="1">
-      <x:c r="A5" s="10">
+      <x:c r="A5" s="10" t="d">
+        <x:v>2026-10-31T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B5" s="11" t="str">
+        <x:v>토</x:v>
+      </x:c>
+      <x:c r="C5" s="11" t="str">
+        <x:v>Part 3</x:v>
+      </x:c>
+      <x:c r="D5" s="11" t="str">
+        <x:v>1일차 약 33%</x:v>
+      </x:c>
+      <x:c r="E5" s="12" t="str">
+        <x:v>CNN / VGG·ResNet / 개 품종 분류 시작</x:v>
+      </x:c>
+      <x:c r="F5" s="13" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G5" s="13" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="34.04999923706055" customHeight="1">
+      <x:c r="A6" s="10" t="d">
+        <x:v>2026-11-01T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="str">
+        <x:v>일</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="str">
+        <x:v>Part 3</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="str">
+        <x:v>2일차 약 33%</x:v>
+      </x:c>
+      <x:c r="E6" s="12" t="str">
+        <x:v>개 품종 분류 마무리 / 흉부 X-ray 전반</x:v>
+      </x:c>
+      <x:c r="F6" s="13" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G6" s="13"/>
+    </x:row>
+    <x:row r="7" ht="34.04999923706055" customHeight="1">
+      <x:c r="A7" s="50" t="d">
+        <x:v>2026-11-02T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B7" s="51" t="str">
+        <x:v>월</x:v>
+      </x:c>
+      <x:c r="C7" s="51" t="str">
+        <x:v>Part 3</x:v>
+      </x:c>
+      <x:c r="D7" s="51" t="str">
+        <x:v>3일차 약 34%</x:v>
+      </x:c>
+      <x:c r="E7" s="52" t="str">
+        <x:v>흉부 X-ray 마무리 / 자연 풍경 이미지 분류</x:v>
+      </x:c>
+      <x:c r="F7" s="53" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G7" s="53"/>
+    </x:row>
+    <x:row r="8" ht="34.04999923706055" customHeight="1">
+      <x:c r="A8" s="42" t="d">
+        <x:v>2026-11-03T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B8" s="43" t="str">
+        <x:v>화</x:v>
+      </x:c>
+      <x:c r="C8" s="43" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D8" s="43" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E8" s="44" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F8" s="45">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G8" s="45"/>
+    </x:row>
+    <x:row r="9" ht="34.04999923706055" customHeight="1">
+      <x:c r="A9" s="42" t="d">
+        <x:v>2026-11-04T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B9" s="43" t="str">
+        <x:v>수</x:v>
+      </x:c>
+      <x:c r="C9" s="43" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D9" s="43" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E9" s="44" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F9" s="45">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G9" s="45"/>
+    </x:row>
+    <x:row r="10" ht="34.04999923706055" customHeight="1">
+      <x:c r="A10" s="42" t="d">
+        <x:v>2026-11-05T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B10" s="43" t="str">
+        <x:v>목</x:v>
+      </x:c>
+      <x:c r="C10" s="43" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D10" s="43" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E10" s="44" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F10" s="45">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G10" s="45"/>
+    </x:row>
+    <x:row r="11" ht="34.04999923706055" customHeight="1">
+      <x:c r="A11" s="46" t="d">
+        <x:v>2026-11-06T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B11" s="47" t="str">
+        <x:v>금</x:v>
+      </x:c>
+      <x:c r="C11" s="47" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D11" s="47" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E11" s="48" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F11" s="49">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G11" s="49"/>
+    </x:row>
+    <x:row r="12" ht="34.04999923706055" customHeight="1">
+      <x:c r="A12" s="46" t="d">
+        <x:v>2026-11-07T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B12" s="47" t="str">
+        <x:v>토</x:v>
+      </x:c>
+      <x:c r="C12" s="47" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D12" s="47" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E12" s="48" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F12" s="49">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G12" s="49"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="46" t="d">
+        <x:v>2026-11-08T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B13" s="47" t="str">
+        <x:v>일</x:v>
+      </x:c>
+      <x:c r="C13" s="47" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D13" s="47" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E13" s="48" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F13" s="49">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G13" s="49"/>
+    </x:row>
+    <x:row r="14" ht="30" customHeight="1">
+      <x:c r="A14"/>
+      <x:c r="B14"/>
+      <x:c r="C14"/>
+      <x:c r="D14"/>
+      <x:c r="E14"/>
+      <x:c r="F14"/>
+      <x:c r="G14"/>
+    </x:row>
+    <x:row r="15" ht="28.049999237060547" customHeight="1">
+      <x:c r="A15" s="32" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B15" s="32"/>
+      <x:c r="C15" s="32"/>
+      <x:c r="D15" s="32"/>
+      <x:c r="E15" s="32"/>
+      <x:c r="F15" s="32"/>
+      <x:c r="G15" s="32"/>
+    </x:row>
+    <x:row r="16" ht="34.04999923706055" customHeight="1">
+      <x:c r="A16" s="33" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B16" s="33" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D16" s="33" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E16" s="33" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F16" s="33" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G16" s="33" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="34.04999923706055" customHeight="1">
+      <x:c r="A17" s="34">
+        <x:v>46323</x:v>
+      </x:c>
+      <x:c r="B17" s="35" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C17" s="35" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D17" s="35" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E17" s="36" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="F17" s="37">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G17" s="37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="34.04999923706055" customHeight="1">
+      <x:c r="A18" s="38">
+        <x:v>46324</x:v>
+      </x:c>
+      <x:c r="B18" s="39" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C18" s="39" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D18" s="39" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E18" s="40" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F18" s="41">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G18" s="41" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="34.04999923706055" customHeight="1">
+      <x:c r="A19" s="34">
+        <x:v>46325</x:v>
+      </x:c>
+      <x:c r="B19" s="35" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C19" s="35" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D19" s="35" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E19" s="36" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F19" s="37">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G19" s="37" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="34.04999923706055" customHeight="1">
+      <x:c r="A20" s="38">
         <x:v>46326</x:v>
       </x:c>
-      <x:c r="B5" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C5" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D5" s="11" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E5" s="12" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F5" s="13">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G5" s="13"/>
-    </x:row>
-    <x:row r="6" ht="34.04999923706055" customHeight="1">
-      <x:c r="A6" s="10">
+      <x:c r="B20" s="39" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C20" s="39" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D20" s="39" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E20" s="40" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F20" s="41">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G20" s="41" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="34.04999923706055" customHeight="1">
+      <x:c r="A21" s="34">
         <x:v>46327</x:v>
       </x:c>
-      <x:c r="B6" s="11" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E6" s="12" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F6" s="13">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G6" s="13"/>
-    </x:row>
-    <x:row r="7" ht="34.04999923706055" customHeight="1">
-      <x:c r="A7" s="14">
+      <x:c r="B21" s="35" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C21" s="35" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D21" s="35" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E21" s="36" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F21" s="37">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G21" s="37"/>
+    </x:row>
+    <x:row r="22" ht="34.04999923706055" customHeight="1">
+      <x:c r="A22" s="38">
         <x:v>46328</x:v>
       </x:c>
-      <x:c r="B7" s="15" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C7" s="15" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D7" s="15" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E7" s="16" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="F7" s="17">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G7" s="17"/>
-    </x:row>
-    <x:row r="8" ht="34.04999923706055" customHeight="1">
-      <x:c r="A8" s="14">
+      <x:c r="B22" s="39" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C22" s="39" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D22" s="39" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E22" s="40" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F22" s="41">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G22" s="41"/>
+    </x:row>
+    <x:row r="23" ht="34.04999923706055" customHeight="1">
+      <x:c r="A23" s="34">
         <x:v>46329</x:v>
       </x:c>
-      <x:c r="B8" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C8" s="15" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D8" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E8" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F8" s="17">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G8" s="17"/>
-    </x:row>
-    <x:row r="9" ht="34.04999923706055" customHeight="1">
-      <x:c r="A9" s="14">
+      <x:c r="B23" s="35" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C23" s="35" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D23" s="35" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E23" s="36" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F23" s="37">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G23" s="37"/>
+    </x:row>
+    <x:row r="24" ht="34.04999923706055" customHeight="1">
+      <x:c r="A24" s="38">
         <x:v>46330</x:v>
       </x:c>
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B24" s="39" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D9" s="15" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E9" s="16" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="F9" s="17">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G9" s="17"/>
-    </x:row>
-    <x:row r="10" ht="34.04999923706055" customHeight="1">
-      <x:c r="A10" s="18">
+      <x:c r="C24" s="39" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D24" s="39" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E24" s="40" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="F24" s="41">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G24" s="41"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="34">
         <x:v>46331</x:v>
       </x:c>
-      <x:c r="B10" s="19" t="s">
+      <x:c r="B25" s="35" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C10" s="19" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D10" s="19" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E10" s="20" t="s">
+      <x:c r="C25" s="35" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D25" s="35" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="F10" s="21">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G10" s="21"/>
-    </x:row>
-    <x:row r="11" ht="34.04999923706055" customHeight="1">
-      <x:c r="A11" s="18">
-        <x:v>46332</x:v>
-      </x:c>
-      <x:c r="B11" s="19" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C11" s="19" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D11" s="19" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E11" s="20" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="F11" s="21">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G11" s="21"/>
-    </x:row>
-    <x:row r="12" ht="34.04999923706055" customHeight="1">
-      <x:c r="A12" s="18">
-        <x:v>46333</x:v>
-      </x:c>
-      <x:c r="B12" s="19" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C12" s="19" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D12" s="19" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="E12" s="20" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="F12" s="21">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G12" s="21"/>
-    </x:row>
-    <x:row r="14" ht="30" customHeight="1">
-      <x:c r="A14" s="22" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="B14" s="22"/>
-      <x:c r="C14" s="22"/>
-      <x:c r="D14" s="22"/>
-      <x:c r="E14" s="22"/>
-      <x:c r="F14" s="22"/>
-      <x:c r="G14" s="22"/>
-    </x:row>
-    <x:row r="15" ht="28.049999237060547" customHeight="1">
-      <x:c r="A15" s="23" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B15" s="23" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C15" s="23" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="D15" s="23" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E15" s="23" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F15" s="23" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G15" s="23" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="34.04999923706055" customHeight="1">
-      <x:c r="A16" s="24">
-        <x:v>46323</x:v>
-      </x:c>
-      <x:c r="B16" s="25" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C16" s="25" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D16" s="25" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E16" s="26" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="F16" s="27">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G16" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="34.04999923706055" customHeight="1">
-      <x:c r="A17" s="28">
-        <x:v>46324</x:v>
-      </x:c>
-      <x:c r="B17" s="29" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C17" s="29" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D17" s="29" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E17" s="30" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="F17" s="31">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G17" s="31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="34.04999923706055" customHeight="1">
-      <x:c r="A18" s="24">
-        <x:v>46325</x:v>
-      </x:c>
-      <x:c r="B18" s="25" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C18" s="25" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D18" s="25" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E18" s="26" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="F18" s="27">
+      <x:c r="E25" s="36" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F25" s="37">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G18" s="27" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="34.04999923706055" customHeight="1">
-      <x:c r="A19" s="28">
-        <x:v>46326</x:v>
-      </x:c>
-      <x:c r="B19" s="29" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C19" s="29" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="D19" s="29" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E19" s="30" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="F19" s="31">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G19" s="31"/>
-    </x:row>
-    <x:row r="20" ht="34.04999923706055" customHeight="1">
-      <x:c r="A20" s="24">
-        <x:v>46327</x:v>
-      </x:c>
-      <x:c r="B20" s="25" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C20" s="25" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="D20" s="25" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E20" s="26" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F20" s="27">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G20" s="27"/>
-    </x:row>
-    <x:row r="21" ht="34.04999923706055" customHeight="1">
-      <x:c r="A21" s="28">
-        <x:v>46328</x:v>
-      </x:c>
-      <x:c r="B21" s="29" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C21" s="29" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D21" s="29" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E21" s="30" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="F21" s="31">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G21" s="31"/>
-    </x:row>
-    <x:row r="22" ht="34.04999923706055" customHeight="1">
-      <x:c r="A22" s="24">
-        <x:v>46329</x:v>
-      </x:c>
-      <x:c r="B22" s="25" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C22" s="25" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D22" s="25" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E22" s="26" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="F22" s="27">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G22" s="27"/>
-    </x:row>
-    <x:row r="23" ht="34.04999923706055" customHeight="1">
-      <x:c r="A23" s="28">
-        <x:v>46330</x:v>
-      </x:c>
-      <x:c r="B23" s="29" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C23" s="29" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D23" s="29" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E23" s="30" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="F23" s="31">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G23" s="31"/>
-    </x:row>
-    <x:row r="24" ht="34.04999923706055" customHeight="1">
-      <x:c r="A24" s="24">
-        <x:v>46331</x:v>
-      </x:c>
-      <x:c r="B24" s="25" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C24" s="25" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="D24" s="25" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E24" s="26" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="F24" s="27">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G24" s="27"/>
+      <x:c r="G25" s="37"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
